--- a/Classement_2.xlsx
+++ b/Classement_2.xlsx
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.008587962962962962</v>
+        <v>0.00869212962962963</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.008587962962962962</v>
+        <v>0.00880787037037037</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.008587962962962962</v>
+        <v>0.00880787037037037</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.008599537037037037</v>
+        <v>0.00880787037037037</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.008599537037037037</v>
+        <v>0.008877314814814815</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.008622685185185185</v>
+        <v>0.008958333333333334</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.008645833333333333</v>
+        <v>0.008958333333333334</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.008668981481481481</v>
+        <v>0.009027777777777777</v>
       </c>
       <c r="G44" s="2" t="n"/>
       <c r="H44" s="3" t="n"/>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.008680555555555556</v>
+        <v>0.009027777777777777</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.008680555555555556</v>
+        <v>0.009155092592592593</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.008726851851851852</v>
+        <v>0.009282407407407408</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.008738425925925926</v>
+        <v>0.009282407407407408</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.008738425925925926</v>
+        <v>0.009340277777777777</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.008796296296296297</v>
+        <v>0.009398148148148149</v>
       </c>
       <c r="G50" s="2" t="n"/>
       <c r="H50" s="3" t="n"/>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.008796296296296297</v>
+        <v>0.009398148148148149</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.008819444444444444</v>
+        <v>0.009456018518518518</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.008819444444444444</v>
+        <v>0.009525462962962963</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.008819444444444444</v>
+        <v>0.009606481481481481</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0.008819444444444444</v>
+        <v>0.009606481481481481</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.008831018518518519</v>
+        <v>0.009699074074074074</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.008831018518518519</v>
+        <v>0.009699074074074074</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>0.008831018518518519</v>
+        <v>0.009699074074074074</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.008831018518518519</v>
+        <v>0.009768518518518518</v>
       </c>
       <c r="G59" s="2" t="n"/>
       <c r="H59" s="3" t="n"/>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.008842592592592593</v>
+        <v>0.009814814814814814</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>0.008854166666666666</v>
+        <v>0.009895833333333333</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.008900462962962962</v>
+        <v>0.009895833333333333</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.008923611111111111</v>
+        <v>0.009965277777777778</v>
       </c>
       <c r="G63" s="2" t="n"/>
       <c r="H63" s="3" t="n"/>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.008923611111111111</v>
+        <v>0.009965277777777778</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>0.008946759259259258</v>
+        <v>0.009965277777777778</v>
       </c>
       <c r="G65" s="2" t="n"/>
       <c r="H65" s="3" t="n"/>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.008946759259259258</v>
+        <v>0.009965277777777778</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>0.008958333333333334</v>
+        <v>0.01005787037037037</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>0.008969907407407407</v>
+        <v>0.01005787037037037</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>0.008969907407407407</v>
+        <v>0.01018518518518519</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>0.008969907407407407</v>
+        <v>0.01018518518518519</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>0.008993055555555556</v>
+        <v>0.01028935185185185</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>0.009016203703703703</v>
+        <v>0.01028935185185185</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>0.009016203703703703</v>
+        <v>0.01028935185185185</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>0.009027777777777777</v>
+        <v>0.01028935185185185</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>0.009027777777777777</v>
+        <v>0.01038194444444444</v>
       </c>
       <c r="G75" s="2" t="n"/>
       <c r="H75" s="3" t="n"/>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>0.009027777777777777</v>
+        <v>0.01047453703703704</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>0.009062499999999999</v>
+        <v>0.01047453703703704</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0.009085648148148148</v>
+        <v>0.01047453703703704</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0.009085648148148148</v>
+        <v>0.01047453703703704</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>0.009131944444444444</v>
+        <v>0.0105787037037037</v>
       </c>
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="3" t="inlineStr">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0.009131944444444444</v>
+        <v>0.010625</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>0.009131944444444444</v>
+        <v>0.01075231481481482</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0.009143518518518518</v>
+        <v>0.01085648148148148</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0.009143518518518518</v>
+        <v>0.0109837962962963</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>0.009143518518518518</v>
+        <v>0.0109837962962963</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>0.009143518518518518</v>
+        <v>0.0109837962962963</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>0.009155092592592593</v>
+        <v>0.01108796296296296</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>0.009155092592592593</v>
+        <v>0.01116898148148148</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>0.009189814814814816</v>
+        <v>0.01116898148148148</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>0.009212962962962963</v>
+        <v>0.01125</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>0.009247685185185185</v>
+        <v>0.01125</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>0.009247685185185185</v>
+        <v>0.0112962962962963</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>0.009247685185185185</v>
+        <v>0.0112962962962963</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>0.009270833333333334</v>
+        <v>0.01140046296296296</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>0.009270833333333334</v>
+        <v>0.01140046296296296</v>
       </c>
       <c r="G95" s="2" t="n"/>
       <c r="H95" s="3" t="n"/>
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>0.009270833333333334</v>
+        <v>0.01144675925925926</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>0.009270833333333334</v>
+        <v>0.01149305555555555</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>0.009293981481481481</v>
+        <v>0.0115625</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>0.009293981481481481</v>
+        <v>0.01162037037037037</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>0.009293981481481481</v>
+        <v>0.01162037037037037</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>0.00931712962962963</v>
+        <v>0.01162037037037037</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>0.00931712962962963</v>
+        <v>0.01168981481481481</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>0.009340277777777777</v>
+        <v>0.01168981481481481</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>0.009340277777777777</v>
+        <v>0.01173611111111111</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>0.009340277777777777</v>
+        <v>0.01178240740740741</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>0.009398148148148149</v>
+        <v>0.01178240740740741</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>0.009398148148148149</v>
+        <v>0.01184027777777778</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="F108" s="4" t="n">
-        <v>0.009432870370370371</v>
+        <v>0.01184027777777778</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>0.009467592592592593</v>
+        <v>0.01188657407407407</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>0.009467592592592593</v>
+        <v>0.01196759259259259</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>0.009525462962962963</v>
+        <v>0.01196759259259259</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>0.009525462962962963</v>
+        <v>0.01196759259259259</v>
       </c>
       <c r="G112" s="2" t="n"/>
       <c r="H112" s="3" t="n"/>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>0.009525462962962963</v>
+        <v>0.01201388888888889</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>0.009537037037037037</v>
+        <v>0.01201388888888889</v>
       </c>
       <c r="G114" s="2" t="n"/>
       <c r="H114" s="3" t="n"/>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>0.009537037037037037</v>
+        <v>0.01201388888888889</v>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>0.009571759259259259</v>
+        <v>0.01212962962962963</v>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>0.009594907407407408</v>
+        <v>0.0122337962962963</v>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>0.009606481481481481</v>
+        <v>0.0122337962962963</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>0.009641203703703704</v>
+        <v>0.01228009259259259</v>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>0.009652777777777777</v>
+        <v>0.01228009259259259</v>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>0.009652777777777777</v>
+        <v>0.01234953703703704</v>
       </c>
       <c r="G121" s="2" t="n"/>
       <c r="H121" s="3" t="n"/>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>0.009699074074074074</v>
+        <v>0.01234953703703704</v>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>0.009722222222222222</v>
+        <v>0.01234953703703704</v>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="F124" s="4" t="n">
-        <v>0.009722222222222222</v>
+        <v>0.01234953703703704</v>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>0.009768518518518518</v>
+        <v>0.01241898148148148</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>0.009768518518518518</v>
+        <v>0.01241898148148148</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>0.009768518518518518</v>
+        <v>0.01241898148148148</v>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="F128" s="4" t="n">
-        <v>0.009814814814814814</v>
+        <v>0.0125</v>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>0.009837962962962963</v>
+        <v>0.01255787037037037</v>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="F130" s="4" t="n">
-        <v>0.009837962962962963</v>
+        <v>0.01255787037037037</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>0.009884259259259259</v>
+        <v>0.01255787037037037</v>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="F132" s="4" t="n">
-        <v>0.009884259259259259</v>
+        <v>0.01255787037037037</v>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>0.009884259259259259</v>
+        <v>0.01267361111111111</v>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>0.009884259259259259</v>
+        <v>0.01280092592592593</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>0.009895833333333333</v>
+        <v>0.01280092592592593</v>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="F136" s="4" t="n">
-        <v>0.009907407407407408</v>
+        <v>0.01288194444444444</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>0.009930555555555555</v>
+        <v>0.01288194444444444</v>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="F138" s="4" t="n">
-        <v>0.009930555555555555</v>
+        <v>0.01288194444444444</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>0.009942129629629629</v>
+        <v>0.01297453703703704</v>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="F140" s="4" t="n">
-        <v>0.009965277777777778</v>
+        <v>0.01302083333333333</v>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="F141" s="4" t="n">
-        <v>0.009965277777777778</v>
+        <v>0.01302083333333333</v>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="F142" s="4" t="n">
-        <v>0.009988425925925927</v>
+        <v>0.0130787037037037</v>
       </c>
       <c r="G142" s="2" t="n"/>
       <c r="H142" s="3" t="n"/>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="F143" s="4" t="n">
-        <v>0.009988425925925927</v>
+        <v>0.01314814814814815</v>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="F144" s="4" t="n">
-        <v>0.009988425925925927</v>
+        <v>0.01314814814814815</v>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="F145" s="4" t="n">
-        <v>0.009988425925925927</v>
+        <v>0.01314814814814815</v>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="F146" s="4" t="n">
-        <v>0.01002314814814815</v>
+        <v>0.01321759259259259</v>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="F147" s="4" t="n">
-        <v>0.01002314814814815</v>
+        <v>0.01321759259259259</v>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         </is>
       </c>
       <c r="F148" s="4" t="n">
-        <v>0.01005787037037037</v>
+        <v>0.01321759259259259</v>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="F149" s="4" t="n">
-        <v>0.01005787037037037</v>
+        <v>0.01333333333333333</v>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="F150" s="4" t="n">
-        <v>0.01005787037037037</v>
+        <v>0.01333333333333333</v>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="F151" s="4" t="n">
-        <v>0.01006944444444445</v>
+        <v>0.0133912037037037</v>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="F152" s="4" t="n">
-        <v>0.01006944444444445</v>
+        <v>0.0133912037037037</v>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="F153" s="4" t="n">
-        <v>0.01006944444444445</v>
+        <v>0.0133912037037037</v>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="F154" s="4" t="n">
-        <v>0.01006944444444445</v>
+        <v>0.0133912037037037</v>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="F155" s="4" t="n">
-        <v>0.01010416666666667</v>
+        <v>0.01342592592592593</v>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="F156" s="4" t="n">
-        <v>0.01010416666666667</v>
+        <v>0.01355324074074074</v>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="F157" s="4" t="n">
-        <v>0.01010416666666667</v>
+        <v>0.01355324074074074</v>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="F158" s="4" t="n">
-        <v>0.01010416666666667</v>
+        <v>0.01355324074074074</v>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="F159" s="4" t="n">
-        <v>0.01013888888888889</v>
+        <v>0.01364583333333333</v>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="F160" s="4" t="n">
-        <v>0.01013888888888889</v>
+        <v>0.01364583333333333</v>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>0.01016203703703704</v>
+        <v>0.0137037037037037</v>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="F162" s="4" t="n">
-        <v>0.01019675925925926</v>
+        <v>0.0137037037037037</v>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F163" s="4" t="n">
-        <v>0.01020833333333333</v>
+        <v>0.0137962962962963</v>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="F164" s="4" t="n">
-        <v>0.01021990740740741</v>
+        <v>0.0137962962962963</v>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="E165" s="3" t="n"/>
       <c r="F165" s="4" t="n">
-        <v>0.01023148148148148</v>
+        <v>0.01384259259259259</v>
       </c>
       <c r="G165" s="2" t="n"/>
       <c r="H165" s="3" t="n"/>
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="F166" s="4" t="n">
-        <v>0.01024305555555556</v>
+        <v>0.01384259259259259</v>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="F167" s="4" t="n">
-        <v>0.0102662037037037</v>
+        <v>0.01384259259259259</v>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="F168" s="4" t="n">
-        <v>0.0103125</v>
+        <v>0.01393518518518519</v>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="F169" s="4" t="n">
-        <v>0.0103125</v>
+        <v>0.01393518518518519</v>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="F170" s="4" t="n">
-        <v>0.01032407407407407</v>
+        <v>0.01393518518518519</v>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         </is>
       </c>
       <c r="F171" s="4" t="n">
-        <v>0.01034722222222222</v>
+        <v>0.01393518518518519</v>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="F172" s="4" t="n">
-        <v>0.01034722222222222</v>
+        <v>0.0140625</v>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="F173" s="4" t="n">
-        <v>0.0103587962962963</v>
+        <v>0.0140625</v>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="F174" s="4" t="n">
-        <v>0.0103587962962963</v>
+        <v>0.01417824074074074</v>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="F175" s="4" t="n">
-        <v>0.0103587962962963</v>
+        <v>0.01417824074074074</v>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="F176" s="4" t="n">
-        <v>0.01041666666666667</v>
+        <v>0.01417824074074074</v>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         </is>
       </c>
       <c r="F177" s="4" t="n">
-        <v>0.01041666666666667</v>
+        <v>0.01428240740740741</v>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="F178" s="4" t="n">
-        <v>0.01043981481481481</v>
+        <v>0.01435185185185185</v>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="F179" s="4" t="n">
-        <v>0.01045138888888889</v>
+        <v>0.01435185185185185</v>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="F180" s="4" t="n">
-        <v>0.01046296296296296</v>
+        <v>0.01435185185185185</v>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="F181" s="4" t="n">
-        <v>0.01046296296296296</v>
+        <v>0.0144212962962963</v>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         </is>
       </c>
       <c r="F182" s="4" t="n">
-        <v>0.01046296296296296</v>
+        <v>0.0144212962962963</v>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="F183" s="4" t="n">
-        <v>0.01047453703703704</v>
+        <v>0.01447916666666667</v>
       </c>
       <c r="G183" s="2" t="n"/>
       <c r="H183" s="3" t="n"/>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="F184" s="4" t="n">
-        <v>0.01053240740740741</v>
+        <v>0.01447916666666667</v>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="F185" s="4" t="n">
-        <v>0.01053240740740741</v>
+        <v>0.01447916666666667</v>
       </c>
       <c r="G185" s="2" t="n"/>
       <c r="H185" s="3" t="n"/>
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="F186" s="4" t="n">
-        <v>0.01054398148148148</v>
+        <v>0.01447916666666667</v>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="F187" s="4" t="n">
-        <v>0.01054398148148148</v>
+        <v>0.01459490740740741</v>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="F188" s="4" t="n">
-        <v>0.01055555555555556</v>
+        <v>0.01459490740740741</v>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="F189" s="4" t="n">
-        <v>0.01055555555555556</v>
+        <v>0.01459490740740741</v>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="F190" s="4" t="n">
-        <v>0.01061342592592593</v>
+        <v>0.01467592592592593</v>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="F191" s="4" t="n">
-        <v>0.01061342592592593</v>
+        <v>0.01479166666666667</v>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F192" s="4" t="n">
-        <v>0.01061342592592593</v>
+        <v>0.01479166666666667</v>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="F193" s="4" t="n">
-        <v>0.01061342592592593</v>
+        <v>0.01486111111111111</v>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="F194" s="4" t="n">
-        <v>0.01064814814814815</v>
+        <v>0.01486111111111111</v>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="F195" s="4" t="n">
-        <v>0.0106712962962963</v>
+        <v>0.01486111111111111</v>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="F196" s="4" t="n">
-        <v>0.01070601851851852</v>
+        <v>0.01493055555555556</v>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="F197" s="4" t="n">
-        <v>0.01070601851851852</v>
+        <v>0.0150462962962963</v>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="F198" s="4" t="n">
-        <v>0.01074074074074074</v>
+        <v>0.0150462962962963</v>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         </is>
       </c>
       <c r="F199" s="4" t="n">
-        <v>0.01075231481481482</v>
+        <v>0.01517361111111111</v>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="F200" s="4" t="n">
-        <v>0.01075231481481482</v>
+        <v>0.01528935185185185</v>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="F201" s="4" t="n">
-        <v>0.01075231481481482</v>
+        <v>0.01540509259259259</v>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="F202" s="4" t="n">
-        <v>0.01081018518518518</v>
+        <v>0.01552083333333333</v>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="F203" s="4" t="n">
-        <v>0.01081018518518518</v>
+        <v>0.01552083333333333</v>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="F204" s="4" t="n">
-        <v>0.01081018518518518</v>
+        <v>0.01552083333333333</v>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="F205" s="4" t="n">
-        <v>0.01081018518518518</v>
+        <v>0.015625</v>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="F206" s="4" t="n">
-        <v>0.01085648148148148</v>
+        <v>0.01568287037037037</v>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="F207" s="4" t="n">
-        <v>0.01085648148148148</v>
+        <v>0.01577546296296296</v>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="F208" s="4" t="n">
-        <v>0.01085648148148148</v>
+        <v>0.01577546296296296</v>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         </is>
       </c>
       <c r="F209" s="4" t="n">
-        <v>0.0108912037037037</v>
+        <v>0.01584490740740741</v>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="F210" s="4" t="n">
-        <v>0.01091435185185185</v>
+        <v>0.01584490740740741</v>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="F211" s="4" t="n">
-        <v>0.01091435185185185</v>
+        <v>0.01584490740740741</v>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="F212" s="4" t="n">
-        <v>0.01092592592592593</v>
+        <v>0.01584490740740741</v>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="F213" s="4" t="n">
-        <v>0.0109375</v>
+        <v>0.0158912037037037</v>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="F214" s="4" t="n">
-        <v>0.01097222222222222</v>
+        <v>0.0159375</v>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="F215" s="4" t="n">
-        <v>0.01097222222222222</v>
+        <v>0.0159375</v>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="F216" s="4" t="n">
-        <v>0.01097222222222222</v>
+        <v>0.01600694444444445</v>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="F217" s="4" t="n">
-        <v>0.01097222222222222</v>
+        <v>0.01600694444444445</v>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="F218" s="4" t="n">
-        <v>0.01099537037037037</v>
+        <v>0.01607638888888889</v>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         </is>
       </c>
       <c r="F219" s="4" t="n">
-        <v>0.01099537037037037</v>
+        <v>0.01607638888888889</v>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="F220" s="4" t="n">
-        <v>0.01099537037037037</v>
+        <v>0.01607638888888889</v>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>

--- a/Classement_2.xlsx
+++ b/Classement_2.xlsx
@@ -741,8 +741,16 @@
       <c r="F8" s="4" t="n">
         <v>0.006863425925925926</v>
       </c>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="3" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Junior M</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1057,8 +1065,16 @@
       <c r="F17" s="4" t="n">
         <v>0.007326388888888889</v>
       </c>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="3" t="n"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Sénior M</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1157,10 +1173,14 @@
       <c r="F20" s="4" t="n">
         <v>0.007627314814814815</v>
       </c>
-      <c r="G20" s="2" t="n"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Minime 2 M</t>
+          <t>Sénior M</t>
         </is>
       </c>
     </row>
@@ -1509,10 +1529,14 @@
       <c r="F30" s="4" t="n">
         <v>0.008090277777777778</v>
       </c>
-      <c r="G30" s="2" t="n"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Minime 2 M</t>
+          <t>Sénior M</t>
         </is>
       </c>
     </row>
@@ -1577,10 +1601,14 @@
       <c r="F32" s="4" t="n">
         <v>0.008287037037037037</v>
       </c>
-      <c r="G32" s="2" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Minime 2 M</t>
+          <t>Sénior M</t>
         </is>
       </c>
     </row>
@@ -2005,8 +2033,16 @@
       <c r="F44" s="4" t="n">
         <v>0.009027777777777777</v>
       </c>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="3" t="n"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Junior M</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2213,8 +2249,16 @@
       <c r="F50" s="4" t="n">
         <v>0.009398148148148149</v>
       </c>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="3" t="n"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Junior M</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -2529,8 +2573,16 @@
       <c r="F59" s="4" t="n">
         <v>0.009768518518518518</v>
       </c>
-      <c r="G59" s="2" t="n"/>
-      <c r="H59" s="3" t="n"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Junior M</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -2665,8 +2717,16 @@
       <c r="F63" s="4" t="n">
         <v>0.009965277777777778</v>
       </c>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="3" t="n"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Junior M</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -2729,8 +2789,16 @@
       <c r="F65" s="4" t="n">
         <v>0.009965277777777778</v>
       </c>
-      <c r="G65" s="2" t="n"/>
-      <c r="H65" s="3" t="n"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Junior M</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3081,8 +3149,16 @@
       <c r="F75" s="4" t="n">
         <v>0.01038194444444444</v>
       </c>
-      <c r="G75" s="2" t="n"/>
-      <c r="H75" s="3" t="n"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Junior M</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -3253,10 +3329,14 @@
       <c r="F80" s="4" t="n">
         <v>0.0105787037037037</v>
       </c>
-      <c r="G80" s="2" t="n"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>Cadet M</t>
+          <t>Sénior M</t>
         </is>
       </c>
     </row>
@@ -3789,8 +3869,16 @@
       <c r="F95" s="4" t="n">
         <v>0.01140046296296296</v>
       </c>
-      <c r="G95" s="2" t="n"/>
-      <c r="H95" s="3" t="n"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>Sénior M</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -4393,8 +4481,16 @@
       <c r="F112" s="4" t="n">
         <v>0.01196759259259259</v>
       </c>
-      <c r="G112" s="2" t="n"/>
-      <c r="H112" s="3" t="n"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>Junior F</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -4457,8 +4553,16 @@
       <c r="F114" s="4" t="n">
         <v>0.01201388888888889</v>
       </c>
-      <c r="G114" s="2" t="n"/>
-      <c r="H114" s="3" t="n"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>Junior F</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -4701,8 +4805,16 @@
       <c r="F121" s="4" t="n">
         <v>0.01234953703703704</v>
       </c>
-      <c r="G121" s="2" t="n"/>
-      <c r="H121" s="3" t="n"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>Sénior M</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -5449,8 +5561,16 @@
       <c r="F142" s="4" t="n">
         <v>0.0130787037037037</v>
       </c>
-      <c r="G142" s="2" t="n"/>
-      <c r="H142" s="3" t="n"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>Junior M</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -6261,7 +6381,11 @@
       <c r="F165" s="4" t="n">
         <v>0.01384259259259259</v>
       </c>
-      <c r="G165" s="2" t="n"/>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="H165" s="3" t="n"/>
     </row>
     <row r="166">
@@ -6901,8 +7025,16 @@
       <c r="F183" s="4" t="n">
         <v>0.01447916666666667</v>
       </c>
-      <c r="G183" s="2" t="n"/>
-      <c r="H183" s="3" t="n"/>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>Junior M</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -6965,8 +7097,16 @@
       <c r="F185" s="4" t="n">
         <v>0.01447916666666667</v>
       </c>
-      <c r="G185" s="2" t="n"/>
-      <c r="H185" s="3" t="n"/>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>Junior F</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">

--- a/Classement_2.xlsx
+++ b/Classement_2.xlsx
@@ -68,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -78,6 +78,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -522,8 +525,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
-        <v>0.006157407407407407</v>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>8:52</t>
+        </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -558,8 +563,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
-        <v>0.006412037037037037</v>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>9:14</t>
+        </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -594,8 +601,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>0.006840277777777778</v>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>9:51</t>
+        </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -630,8 +639,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>0.006851851851851852</v>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>9:52</t>
+        </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -666,8 +677,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>0.006851851851851852</v>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>9:52</t>
+        </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -702,8 +715,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>0.006863425925925926</v>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>9:53</t>
+        </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -738,8 +753,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>0.006863425925925926</v>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>9:53</t>
+        </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -774,8 +791,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>0.006863425925925926</v>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>9:53</t>
+        </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -810,8 +829,10 @@
           <t>1ere STAV</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>0.006863425925925926</v>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>9:53</t>
+        </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -846,8 +867,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>0.006863425925925926</v>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>9:53</t>
+        </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -882,8 +905,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>0.007106481481481482</v>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -918,8 +943,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>0.007106481481481482</v>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -954,8 +981,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>0.007118055555555555</v>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -990,8 +1019,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>0.00730324074074074</v>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -1026,8 +1057,10 @@
           <t>1G</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>0.007314814814814815</v>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1062,8 +1095,10 @@
           <t>GDEA 2 Sco</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>0.007326388888888889</v>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1098,8 +1133,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>0.007615740740740741</v>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1134,8 +1171,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F19" s="4" t="n">
-        <v>0.007627314814814815</v>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1170,8 +1209,10 @@
           <t>ACSE 2 SCO</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n">
-        <v>0.007627314814814815</v>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1206,8 +1247,10 @@
           <t>Prof</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>0.007638888888888889</v>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -1238,8 +1281,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>0.007893518518518518</v>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -1274,8 +1319,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>0.007893518518518518</v>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -1310,8 +1357,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>0.007905092592592592</v>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1346,8 +1395,10 @@
           <t>Tale G</t>
         </is>
       </c>
-      <c r="F25" s="4" t="n">
-        <v>0.007905092592592592</v>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -1382,8 +1433,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>0.007905092592592592</v>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -1418,8 +1471,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F27" s="4" t="n">
-        <v>0.007916666666666667</v>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -1454,8 +1509,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>0.007916666666666667</v>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -1490,8 +1547,10 @@
           <t>Tale G</t>
         </is>
       </c>
-      <c r="F29" s="4" t="n">
-        <v>0.008032407407407408</v>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -1526,8 +1585,10 @@
           <t>ACSE 2 SCO</t>
         </is>
       </c>
-      <c r="F30" s="4" t="n">
-        <v>0.008090277777777778</v>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -1562,8 +1623,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F31" s="4" t="n">
-        <v>0.008275462962962964</v>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -1598,8 +1661,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>0.008287037037037037</v>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -1634,8 +1699,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F33" s="4" t="n">
-        <v>0.008298611111111111</v>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -1670,8 +1737,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F34" s="4" t="n">
-        <v>0.008298611111111111</v>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
@@ -1706,8 +1775,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F35" s="4" t="n">
-        <v>0.008310185185185184</v>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
@@ -1742,8 +1813,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>0.008576388888888889</v>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -1778,8 +1851,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n">
-        <v>0.00869212962962963</v>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -1814,8 +1889,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F38" s="4" t="n">
-        <v>0.00880787037037037</v>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -1850,8 +1927,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F39" s="4" t="n">
-        <v>0.00880787037037037</v>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -1886,8 +1965,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F40" s="4" t="n">
-        <v>0.00880787037037037</v>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -1922,8 +2003,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F41" s="4" t="n">
-        <v>0.008877314814814815</v>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -1958,8 +2041,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F42" s="4" t="n">
-        <v>0.008958333333333334</v>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -1994,8 +2079,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>0.008958333333333334</v>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2030,8 +2117,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F44" s="4" t="n">
-        <v>0.009027777777777777</v>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -2066,8 +2155,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>0.009027777777777777</v>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -2102,8 +2193,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F46" s="4" t="n">
-        <v>0.009155092592592593</v>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -2138,8 +2231,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F47" s="4" t="n">
-        <v>0.009282407407407408</v>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -2174,8 +2269,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F48" s="4" t="n">
-        <v>0.009282407407407408</v>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -2210,8 +2307,10 @@
           <t>Première Pro</t>
         </is>
       </c>
-      <c r="F49" s="4" t="n">
-        <v>0.009340277777777777</v>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -2246,8 +2345,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F50" s="4" t="n">
-        <v>0.009398148148148149</v>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -2282,8 +2383,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F51" s="4" t="n">
-        <v>0.009398148148148149</v>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -2318,8 +2421,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F52" s="4" t="n">
-        <v>0.009456018518518518</v>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -2354,8 +2459,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F53" s="4" t="n">
-        <v>0.009525462962962963</v>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -2390,8 +2497,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F54" s="4" t="n">
-        <v>0.009606481481481481</v>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -2426,8 +2535,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F55" s="4" t="n">
-        <v>0.009606481481481481</v>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -2462,8 +2573,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F56" s="4" t="n">
-        <v>0.009699074074074074</v>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -2498,8 +2611,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F57" s="4" t="n">
-        <v>0.009699074074074074</v>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -2534,8 +2649,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F58" s="4" t="n">
-        <v>0.009699074074074074</v>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -2570,8 +2687,10 @@
           <t>Terminale Pro</t>
         </is>
       </c>
-      <c r="F59" s="4" t="n">
-        <v>0.009768518518518518</v>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -2606,8 +2725,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F60" s="4" t="n">
-        <v>0.009814814814814814</v>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -2642,8 +2763,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F61" s="4" t="n">
-        <v>0.009895833333333333</v>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -2678,8 +2801,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F62" s="4" t="n">
-        <v>0.009895833333333333</v>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -2714,8 +2839,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F63" s="4" t="n">
-        <v>0.009965277777777778</v>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -2750,8 +2877,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F64" s="4" t="n">
-        <v>0.009965277777777778</v>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -2786,8 +2915,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F65" s="4" t="n">
-        <v>0.009965277777777778</v>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -2822,8 +2953,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F66" s="4" t="n">
-        <v>0.009965277777777778</v>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -2858,8 +2991,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F67" s="4" t="n">
-        <v>0.01005787037037037</v>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -2894,8 +3029,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F68" s="4" t="n">
-        <v>0.01005787037037037</v>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -2930,8 +3067,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F69" s="4" t="n">
-        <v>0.01018518518518519</v>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -2966,8 +3105,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F70" s="4" t="n">
-        <v>0.01018518518518519</v>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -3002,8 +3143,10 @@
           <t>Première PRO APP</t>
         </is>
       </c>
-      <c r="F71" s="4" t="n">
-        <v>0.01028935185185185</v>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -3038,8 +3181,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F72" s="4" t="n">
-        <v>0.01028935185185185</v>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -3074,8 +3219,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F73" s="4" t="n">
-        <v>0.01028935185185185</v>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -3110,8 +3257,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F74" s="4" t="n">
-        <v>0.01028935185185185</v>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -3146,8 +3295,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F75" s="4" t="n">
-        <v>0.01038194444444444</v>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -3182,8 +3333,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F76" s="4" t="n">
-        <v>0.01047453703703704</v>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -3218,8 +3371,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F77" s="4" t="n">
-        <v>0.01047453703703704</v>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -3254,8 +3409,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F78" s="4" t="n">
-        <v>0.01047453703703704</v>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -3290,8 +3447,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F79" s="4" t="n">
-        <v>0.01047453703703704</v>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -3326,8 +3485,10 @@
           <t>GDEA 2 Sco</t>
         </is>
       </c>
-      <c r="F80" s="4" t="n">
-        <v>0.0105787037037037</v>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -3362,8 +3523,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F81" s="4" t="n">
-        <v>0.010625</v>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -3398,8 +3561,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F82" s="4" t="n">
-        <v>0.01075231481481482</v>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -3434,8 +3599,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F83" s="4" t="n">
-        <v>0.01085648148148148</v>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -3470,8 +3637,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F84" s="4" t="n">
-        <v>0.0109837962962963</v>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -3506,8 +3675,10 @@
           <t>Tale G</t>
         </is>
       </c>
-      <c r="F85" s="4" t="n">
-        <v>0.0109837962962963</v>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -3542,8 +3713,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F86" s="4" t="n">
-        <v>0.0109837962962963</v>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -3578,8 +3751,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F87" s="4" t="n">
-        <v>0.01108796296296296</v>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -3614,8 +3789,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F88" s="4" t="n">
-        <v>0.01116898148148148</v>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -3650,8 +3827,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F89" s="4" t="n">
-        <v>0.01116898148148148</v>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -3686,8 +3865,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F90" s="4" t="n">
-        <v>0.01125</v>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -3722,8 +3903,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F91" s="4" t="n">
-        <v>0.01125</v>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -3758,8 +3941,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F92" s="4" t="n">
-        <v>0.0112962962962963</v>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -3794,8 +3979,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F93" s="4" t="n">
-        <v>0.0112962962962963</v>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -3830,8 +4017,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F94" s="4" t="n">
-        <v>0.01140046296296296</v>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -3866,8 +4055,10 @@
           <t>ACSE 2 SCO</t>
         </is>
       </c>
-      <c r="F95" s="4" t="n">
-        <v>0.01140046296296296</v>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -3902,8 +4093,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F96" s="4" t="n">
-        <v>0.01144675925925926</v>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -3938,8 +4131,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0.01149305555555555</v>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -3974,8 +4169,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F98" s="4" t="n">
-        <v>0.0115625</v>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -4010,8 +4207,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F99" s="4" t="n">
-        <v>0.01162037037037037</v>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -4046,8 +4245,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F100" s="4" t="n">
-        <v>0.01162037037037037</v>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -4082,8 +4283,10 @@
           <t>GDEA 2 sco</t>
         </is>
       </c>
-      <c r="F101" s="4" t="n">
-        <v>0.01162037037037037</v>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -4118,8 +4321,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F102" s="4" t="n">
-        <v>0.01168981481481481</v>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -4154,8 +4359,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F103" s="4" t="n">
-        <v>0.01168981481481481</v>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -4190,8 +4397,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F104" s="4" t="n">
-        <v>0.01173611111111111</v>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -4226,8 +4435,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F105" s="4" t="n">
-        <v>0.01178240740740741</v>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -4262,8 +4473,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F106" s="4" t="n">
-        <v>0.01178240740740741</v>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -4298,8 +4511,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F107" s="4" t="n">
-        <v>0.01184027777777778</v>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -4334,8 +4549,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F108" s="4" t="n">
-        <v>0.01184027777777778</v>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -4370,8 +4587,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F109" s="4" t="n">
-        <v>0.01188657407407407</v>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -4406,8 +4625,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F110" s="4" t="n">
-        <v>0.01196759259259259</v>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -4442,8 +4663,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F111" s="4" t="n">
-        <v>0.01196759259259259</v>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -4478,8 +4701,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F112" s="4" t="n">
-        <v>0.01196759259259259</v>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -4514,8 +4739,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F113" s="4" t="n">
-        <v>0.01201388888888889</v>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
@@ -4550,8 +4777,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F114" s="4" t="n">
-        <v>0.01201388888888889</v>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -4586,8 +4815,10 @@
           <t>Tale G</t>
         </is>
       </c>
-      <c r="F115" s="4" t="n">
-        <v>0.01201388888888889</v>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
@@ -4622,8 +4853,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F116" s="4" t="n">
-        <v>0.01212962962962963</v>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
@@ -4658,8 +4891,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F117" s="4" t="n">
-        <v>0.0122337962962963</v>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
@@ -4694,8 +4929,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F118" s="4" t="n">
-        <v>0.0122337962962963</v>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
@@ -4730,8 +4967,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F119" s="4" t="n">
-        <v>0.01228009259259259</v>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
@@ -4766,8 +5005,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F120" s="4" t="n">
-        <v>0.01228009259259259</v>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
@@ -4802,8 +5043,10 @@
           <t>ACSE 2 SCO</t>
         </is>
       </c>
-      <c r="F121" s="4" t="n">
-        <v>0.01234953703703704</v>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
@@ -4838,8 +5081,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F122" s="4" t="n">
-        <v>0.01234953703703704</v>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
@@ -4874,8 +5119,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F123" s="4" t="n">
-        <v>0.01234953703703704</v>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
@@ -4910,8 +5157,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F124" s="4" t="n">
-        <v>0.01234953703703704</v>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
@@ -4946,8 +5195,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F125" s="4" t="n">
-        <v>0.01241898148148148</v>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
@@ -4982,8 +5233,10 @@
           <t>GDEA 2 sco</t>
         </is>
       </c>
-      <c r="F126" s="4" t="n">
-        <v>0.01241898148148148</v>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -5018,8 +5271,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F127" s="4" t="n">
-        <v>0.01241898148148148</v>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
@@ -5054,8 +5309,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F128" s="4" t="n">
-        <v>0.0125</v>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
@@ -5090,8 +5347,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F129" s="4" t="n">
-        <v>0.01255787037037037</v>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
@@ -5126,8 +5385,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F130" s="4" t="n">
-        <v>0.01255787037037037</v>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
@@ -5162,8 +5423,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F131" s="4" t="n">
-        <v>0.01255787037037037</v>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
@@ -5198,8 +5461,10 @@
           <t>Tale G</t>
         </is>
       </c>
-      <c r="F132" s="4" t="n">
-        <v>0.01255787037037037</v>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
@@ -5234,8 +5499,10 @@
           <t>GDEA 2 sco</t>
         </is>
       </c>
-      <c r="F133" s="4" t="n">
-        <v>0.01267361111111111</v>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
@@ -5270,8 +5537,10 @@
           <t>GDEA 2 sco</t>
         </is>
       </c>
-      <c r="F134" s="4" t="n">
-        <v>0.01280092592592593</v>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
@@ -5306,8 +5575,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F135" s="4" t="n">
-        <v>0.01280092592592593</v>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
@@ -5342,8 +5613,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F136" s="4" t="n">
-        <v>0.01288194444444444</v>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
@@ -5378,8 +5651,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F137" s="4" t="n">
-        <v>0.01288194444444444</v>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
@@ -5414,8 +5689,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F138" s="4" t="n">
-        <v>0.01288194444444444</v>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
@@ -5450,8 +5727,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F139" s="4" t="n">
-        <v>0.01297453703703704</v>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
@@ -5486,8 +5765,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F140" s="4" t="n">
-        <v>0.01302083333333333</v>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
@@ -5522,8 +5803,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F141" s="4" t="n">
-        <v>0.01302083333333333</v>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
@@ -5558,8 +5841,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F142" s="4" t="n">
-        <v>0.0130787037037037</v>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
@@ -5594,8 +5879,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F143" s="4" t="n">
-        <v>0.01314814814814815</v>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
@@ -5630,8 +5917,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F144" s="4" t="n">
-        <v>0.01314814814814815</v>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
@@ -5666,8 +5955,10 @@
           <t>1ere STAV</t>
         </is>
       </c>
-      <c r="F145" s="4" t="n">
-        <v>0.01314814814814815</v>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
@@ -5702,8 +5993,10 @@
           <t>Tale G</t>
         </is>
       </c>
-      <c r="F146" s="4" t="n">
-        <v>0.01321759259259259</v>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -5738,8 +6031,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F147" s="4" t="n">
-        <v>0.01321759259259259</v>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
@@ -5774,8 +6069,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F148" s="4" t="n">
-        <v>0.01321759259259259</v>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
@@ -5810,8 +6107,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F149" s="4" t="n">
-        <v>0.01333333333333333</v>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
@@ -5846,8 +6145,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F150" s="4" t="n">
-        <v>0.01333333333333333</v>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
@@ -5882,8 +6183,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F151" s="4" t="n">
-        <v>0.0133912037037037</v>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
@@ -5918,8 +6221,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F152" s="4" t="n">
-        <v>0.0133912037037037</v>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
@@ -5954,8 +6259,10 @@
           <t>Prof</t>
         </is>
       </c>
-      <c r="F153" s="4" t="n">
-        <v>0.0133912037037037</v>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
@@ -5986,8 +6293,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F154" s="4" t="n">
-        <v>0.0133912037037037</v>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
@@ -6022,8 +6331,10 @@
           <t>Première PRO APP</t>
         </is>
       </c>
-      <c r="F155" s="4" t="n">
-        <v>0.01342592592592593</v>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
@@ -6058,8 +6369,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F156" s="4" t="n">
-        <v>0.01355324074074074</v>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
@@ -6094,8 +6407,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F157" s="4" t="n">
-        <v>0.01355324074074074</v>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
@@ -6130,8 +6445,10 @@
           <t>Tale G</t>
         </is>
       </c>
-      <c r="F158" s="4" t="n">
-        <v>0.01355324074074074</v>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
@@ -6166,8 +6483,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F159" s="4" t="n">
-        <v>0.01364583333333333</v>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
@@ -6202,8 +6521,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F160" s="4" t="n">
-        <v>0.01364583333333333</v>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
@@ -6238,8 +6559,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F161" s="4" t="n">
-        <v>0.0137037037037037</v>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
@@ -6274,8 +6597,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F162" s="4" t="n">
-        <v>0.0137037037037037</v>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>19:44</t>
+        </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
@@ -6310,8 +6635,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F163" s="4" t="n">
-        <v>0.0137962962962963</v>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
@@ -6346,8 +6673,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F164" s="4" t="n">
-        <v>0.0137962962962963</v>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
@@ -6378,8 +6707,10 @@
         </is>
       </c>
       <c r="E165" s="3" t="n"/>
-      <c r="F165" s="4" t="n">
-        <v>0.01384259259259259</v>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
@@ -6410,8 +6741,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F166" s="4" t="n">
-        <v>0.01384259259259259</v>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
@@ -6446,8 +6779,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F167" s="4" t="n">
-        <v>0.01384259259259259</v>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
@@ -6482,8 +6817,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F168" s="4" t="n">
-        <v>0.01393518518518519</v>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
@@ -6518,8 +6855,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F169" s="4" t="n">
-        <v>0.01393518518518519</v>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
@@ -6554,8 +6893,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F170" s="4" t="n">
-        <v>0.01393518518518519</v>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
@@ -6590,8 +6931,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F171" s="4" t="n">
-        <v>0.01393518518518519</v>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>20:04</t>
+        </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
@@ -6626,8 +6969,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F172" s="4" t="n">
-        <v>0.0140625</v>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
@@ -6662,8 +7007,10 @@
           <t>Première Pro</t>
         </is>
       </c>
-      <c r="F173" s="4" t="n">
-        <v>0.0140625</v>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
@@ -6698,8 +7045,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F174" s="4" t="n">
-        <v>0.01417824074074074</v>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
@@ -6734,8 +7083,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F175" s="4" t="n">
-        <v>0.01417824074074074</v>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
@@ -6770,8 +7121,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F176" s="4" t="n">
-        <v>0.01417824074074074</v>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
@@ -6806,8 +7159,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F177" s="4" t="n">
-        <v>0.01428240740740741</v>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
@@ -6842,8 +7197,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F178" s="4" t="n">
-        <v>0.01435185185185185</v>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
@@ -6878,8 +7235,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F179" s="4" t="n">
-        <v>0.01435185185185185</v>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
@@ -6914,8 +7273,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F180" s="4" t="n">
-        <v>0.01435185185185185</v>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
@@ -6950,8 +7311,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F181" s="4" t="n">
-        <v>0.0144212962962963</v>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
@@ -6986,8 +7349,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F182" s="4" t="n">
-        <v>0.0144212962962963</v>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
@@ -7022,8 +7387,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F183" s="4" t="n">
-        <v>0.01447916666666667</v>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
@@ -7058,8 +7425,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F184" s="4" t="n">
-        <v>0.01447916666666667</v>
+      <c r="F184" s="5" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
@@ -7094,8 +7463,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F185" s="4" t="n">
-        <v>0.01447916666666667</v>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
@@ -7130,8 +7501,10 @@
           <t>Première PRO APP</t>
         </is>
       </c>
-      <c r="F186" s="4" t="n">
-        <v>0.01447916666666667</v>
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
@@ -7166,8 +7539,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F187" s="4" t="n">
-        <v>0.01459490740740741</v>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
@@ -7202,8 +7577,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F188" s="4" t="n">
-        <v>0.01459490740740741</v>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
@@ -7238,8 +7615,10 @@
           <t>Tale G</t>
         </is>
       </c>
-      <c r="F189" s="4" t="n">
-        <v>0.01459490740740741</v>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>21:01</t>
+        </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
@@ -7274,8 +7653,10 @@
           <t>Tale G</t>
         </is>
       </c>
-      <c r="F190" s="4" t="n">
-        <v>0.01467592592592593</v>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
@@ -7310,8 +7691,10 @@
           <t>ACSE 1 demeter</t>
         </is>
       </c>
-      <c r="F191" s="4" t="n">
-        <v>0.01479166666666667</v>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
@@ -7346,8 +7729,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F192" s="4" t="n">
-        <v>0.01479166666666667</v>
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>21:18</t>
+        </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
@@ -7382,8 +7767,10 @@
           <t>Première PRO APP</t>
         </is>
       </c>
-      <c r="F193" s="4" t="n">
-        <v>0.01486111111111111</v>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
@@ -7418,8 +7805,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F194" s="4" t="n">
-        <v>0.01486111111111111</v>
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
@@ -7454,8 +7843,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F195" s="4" t="n">
-        <v>0.01486111111111111</v>
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
@@ -7490,8 +7881,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F196" s="4" t="n">
-        <v>0.01493055555555556</v>
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
@@ -7526,8 +7919,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F197" s="4" t="n">
-        <v>0.0150462962962963</v>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
@@ -7562,8 +7957,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F198" s="4" t="n">
-        <v>0.0150462962962963</v>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
@@ -7598,8 +7995,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F199" s="4" t="n">
-        <v>0.01517361111111111</v>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
@@ -7634,8 +8033,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F200" s="4" t="n">
-        <v>0.01528935185185185</v>
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
@@ -7670,8 +8071,10 @@
           <t>Tale G</t>
         </is>
       </c>
-      <c r="F201" s="4" t="n">
-        <v>0.01540509259259259</v>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
@@ -7706,8 +8109,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F202" s="4" t="n">
-        <v>0.01552083333333333</v>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
@@ -7742,8 +8147,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F203" s="4" t="n">
-        <v>0.01552083333333333</v>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
@@ -7778,8 +8185,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F204" s="4" t="n">
-        <v>0.01552083333333333</v>
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
@@ -7814,8 +8223,10 @@
           <t>Tale STAV</t>
         </is>
       </c>
-      <c r="F205" s="4" t="n">
-        <v>0.015625</v>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
@@ -7850,8 +8261,10 @@
           <t>Tale G</t>
         </is>
       </c>
-      <c r="F206" s="4" t="n">
-        <v>0.01568287037037037</v>
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
@@ -7886,8 +8299,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F207" s="4" t="n">
-        <v>0.01577546296296296</v>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
@@ -7922,8 +8337,10 @@
           <t>ACSE 2 Sco</t>
         </is>
       </c>
-      <c r="F208" s="4" t="n">
-        <v>0.01577546296296296</v>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
@@ -7958,8 +8375,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F209" s="4" t="n">
-        <v>0.01584490740740741</v>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
@@ -7994,8 +8413,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F210" s="4" t="n">
-        <v>0.01584490740740741</v>
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
@@ -8030,8 +8451,10 @@
           <t>ACSE 1 Céres</t>
         </is>
       </c>
-      <c r="F211" s="4" t="n">
-        <v>0.01584490740740741</v>
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
@@ -8066,8 +8489,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F212" s="4" t="n">
-        <v>0.01584490740740741</v>
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>22:49</t>
+        </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
@@ -8102,8 +8527,10 @@
           <t>Tale PRO</t>
         </is>
       </c>
-      <c r="F213" s="4" t="n">
-        <v>0.0158912037037037</v>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>22:53</t>
+        </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
@@ -8138,8 +8565,10 @@
           <t>Tale G</t>
         </is>
       </c>
-      <c r="F214" s="4" t="n">
-        <v>0.0159375</v>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
@@ -8174,8 +8603,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F215" s="4" t="n">
-        <v>0.0159375</v>
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>22:57</t>
+        </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
@@ -8210,8 +8641,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F216" s="4" t="n">
-        <v>0.01600694444444445</v>
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
@@ -8246,8 +8679,10 @@
           <t>ACSE 1 SCO</t>
         </is>
       </c>
-      <c r="F217" s="4" t="n">
-        <v>0.01600694444444445</v>
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
@@ -8282,8 +8717,10 @@
           <t>Première PRO APP</t>
         </is>
       </c>
-      <c r="F218" s="4" t="n">
-        <v>0.01607638888888889</v>
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>23:09</t>
+        </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
@@ -8318,8 +8755,10 @@
           <t>GDEA 1 App</t>
         </is>
       </c>
-      <c r="F219" s="4" t="n">
-        <v>0.01607638888888889</v>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>23:09</t>
+        </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
@@ -8354,8 +8793,10 @@
           <t>GDEA 1 sco</t>
         </is>
       </c>
-      <c r="F220" s="4" t="n">
-        <v>0.01607638888888889</v>
+      <c r="F220" s="5" t="inlineStr">
+        <is>
+          <t>23:09</t>
+        </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
